--- a/buildplan_generator/output/25-069 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-069 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -70,12 +70,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D6E4F0"/>
         <bgColor rgb="00D6E4F0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-059, 25-058, 25-063, 25-071, 25-067</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -635,17 +628,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,8 +713,8 @@
       <c r="E9" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>3</v>
+      <c r="F9" s="9" t="n">
+        <v>2.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -732,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=0.21 (0.20-0.25)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,7 +750,7 @@
       <c r="E10" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2.5-4.5</t>
+          <t>ratio=0.50 (0.20-0.50)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -796,7 +787,7 @@
       <c r="E11" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="9" t="n">
         <v>3</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -806,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.00 (0.83-1.00)</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -833,8 +824,8 @@
       <c r="E12" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>25.5</v>
+      <c r="F12" s="9" t="n">
+        <v>24.5</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -843,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>14.5-30.0</t>
+          <t>ratio=0.82 (0.48-0.94)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -887,8 +878,8 @@
       <c r="E14" s="8" t="n">
         <v>40</v>
       </c>
-      <c r="F14" s="10" t="n">
-        <v>18</v>
+      <c r="F14" s="9" t="n">
+        <v>17.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -897,7 +888,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>13.2-21.5</t>
+          <t>ratio=0.44 (0.41-0.54)</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -924,8 +915,8 @@
       <c r="E15" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>14.5</v>
+      <c r="F15" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -934,7 +925,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>9.0-19.0</t>
+          <t>ratio=0.75 (0.55-0.95)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -978,8 +969,8 @@
       <c r="E17" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F17" s="10" t="n">
-        <v>10</v>
+      <c r="F17" s="9" t="n">
+        <v>11</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -988,7 +979,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>8.0-12.0</t>
+          <t>ratio=1.38 (1.00-1.75)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1032,7 +1023,7 @@
       <c r="E19" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F19" s="10" t="n">
+      <c r="F19" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1042,7 +1033,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1069,8 +1060,8 @@
       <c r="E20" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="F20" s="10" t="n">
-        <v>6.8</v>
+      <c r="F20" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1079,7 +1070,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>5.0-10.0</t>
+          <t>ratio=0.80 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1106,7 +1097,7 @@
       <c r="E21" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="10" t="n">
+      <c r="F21" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1116,7 +1107,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1160,7 +1151,7 @@
       <c r="E23" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="10" t="n">
+      <c r="F23" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1170,7 +1161,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1198,12 +1189,12 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1230,8 +1221,8 @@
       <c r="E25" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>7.5</v>
+      <c r="F25" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1240,7 +1231,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>4.5-8.0</t>
+          <t>ratio=0.67 (0.50-1.11)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1267,8 +1258,8 @@
       <c r="E26" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>8</v>
+      <c r="F26" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1277,7 +1268,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>3.0-10.0</t>
+          <t>ratio=0.54 (0.25-0.83)</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1304,8 +1295,8 @@
       <c r="E27" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F27" s="10" t="n">
-        <v>10</v>
+      <c r="F27" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1314,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>3.0-16.5</t>
+          <t>ratio=0.44 (0.20-0.89)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1356,17 +1347,15 @@
         </is>
       </c>
       <c r="E29" s="8" t="n"/>
-      <c r="F29" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1393,8 +1382,8 @@
       <c r="E30" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="10" t="n">
-        <v>2</v>
+      <c r="F30" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1403,7 +1392,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=3.00 (2.00-3.50)</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1430,7 +1419,7 @@
       <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="10" t="n">
+      <c r="F31" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
@@ -1440,7 +1429,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1467,7 +1456,7 @@
       <c r="E32" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -1477,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1504,7 +1493,7 @@
       <c r="E33" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F33" s="10" t="n">
+      <c r="F33" s="9" t="n">
         <v>6</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
@@ -1514,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>5.0-6.0</t>
+          <t>ratio=1.00 (0.67-1.33)</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1558,7 +1547,7 @@
       <c r="E35" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="10" t="n">
+      <c r="F35" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
@@ -1568,7 +1557,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>1.0-5.5</t>
+          <t>ratio=2.00 (1.00-5.00)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1595,8 +1584,8 @@
       <c r="E36" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="11" t="n">
-        <v>1.5</v>
+      <c r="F36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
@@ -1605,7 +1594,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1632,7 +1621,7 @@
       <c r="E37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="10" t="n">
+      <c r="F37" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
@@ -1642,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1674,12 +1663,12 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1723,8 +1712,8 @@
       <c r="E40" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>4</v>
+      <c r="F40" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1733,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=1.00 (0.60-1.00)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1760,8 +1749,8 @@
       <c r="E41" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>4</v>
+      <c r="F41" s="9" t="n">
+        <v>3.5</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1770,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>2.0-11.0</t>
+          <t>ratio=0.70 (0.40-1.10)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1797,8 +1786,8 @@
       <c r="E42" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F42" s="10" t="n">
-        <v>6</v>
+      <c r="F42" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1807,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=0.81 (0.38-1.00)</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1834,8 +1823,8 @@
       <c r="E43" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F43" s="10" t="n">
-        <v>2</v>
+      <c r="F43" s="9" t="n">
+        <v>2.8</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1844,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>1.5-3.0</t>
+          <t>ratio=0.92 (0.67-1.00)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1871,8 +1860,8 @@
       <c r="E44" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F44" s="10" t="n">
-        <v>4.8</v>
+      <c r="F44" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1881,7 +1870,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>1.8-5.5</t>
+          <t>ratio=0.33 (0.29-0.67)</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1926,12 +1915,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1958,8 +1947,8 @@
       <c r="E47" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>4</v>
+      <c r="F47" s="9" t="n">
+        <v>6.5</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1968,7 +1957,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>3.0-9.5</t>
+          <t>ratio=1.62 (0.75-2.75)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1995,8 +1984,8 @@
       <c r="E48" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>9</v>
+      <c r="F48" s="9" t="n">
+        <v>9.800000000000001</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2005,7 +1994,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>7.5-16.0</t>
+          <t>ratio=1.22 (0.94-1.50)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2032,8 +2021,8 @@
       <c r="E49" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F49" s="10" t="n">
-        <v>14</v>
+      <c r="F49" s="9" t="n">
+        <v>13.8</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2042,7 +2031,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>13.0-27.0</t>
+          <t>ratio=0.76 (0.67-1.64)</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2069,8 +2058,8 @@
       <c r="E50" s="8" t="n">
         <v>6</v>
       </c>
-      <c r="F50" s="10" t="n">
-        <v>5.2</v>
+      <c r="F50" s="9" t="n">
+        <v>4.8</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2079,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>4.0-6.0</t>
+          <t>ratio=0.79 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2106,8 +2095,8 @@
       <c r="E51" s="8" t="n">
         <v>36</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>26</v>
+      <c r="F51" s="9" t="n">
+        <v>24.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2116,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>8.0-28.0</t>
+          <t>ratio=0.68 (0.20-0.72)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2141,17 +2130,15 @@
         </is>
       </c>
       <c r="E52" s="8" t="n"/>
-      <c r="F52" s="11" t="n">
-        <v>1</v>
-      </c>
+      <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2178,7 +2165,7 @@
       <c r="E53" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F53" s="10" t="n">
+      <c r="F53" s="9" t="n">
         <v>7</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
@@ -2188,7 +2175,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>4.0-11.0</t>
+          <t>ratio=1.40 (0.80-2.20)</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2215,8 +2202,8 @@
       <c r="E54" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>16</v>
+      <c r="F54" s="9" t="n">
+        <v>10.5</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2225,7 +2212,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>10.5-58.0</t>
+          <t>ratio=0.88 (0.50-1.17)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2252,8 +2239,8 @@
       <c r="E55" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F55" s="10" t="n">
-        <v>41</v>
+      <c r="F55" s="9" t="n">
+        <v>35</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2262,7 +2249,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>26.0-89.0</t>
+          <t>ratio=1.75 (1.30-2.02)</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2289,8 +2276,8 @@
       <c r="E56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="10" t="n">
-        <v>2.5</v>
+      <c r="F56" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
@@ -2299,7 +2286,7 @@
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.33 (0.33-0.33)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2343,8 +2330,8 @@
       <c r="E58" s="8" t="n">
         <v>48</v>
       </c>
-      <c r="F58" s="10" t="n">
-        <v>50.5</v>
+      <c r="F58" s="9" t="n">
+        <v>49.8</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2353,7 +2340,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>42.0-72.0</t>
+          <t>ratio=1.04 (0.88-1.23)</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2380,8 +2367,8 @@
       <c r="E59" s="8" t="n">
         <v>32</v>
       </c>
-      <c r="F59" s="10" t="n">
-        <v>24</v>
+      <c r="F59" s="9" t="n">
+        <v>21</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2390,7 +2377,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>15.0-27.0</t>
+          <t>ratio=0.66 (0.34-0.78)</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2417,8 +2404,8 @@
       <c r="E60" s="8" t="n">
         <v>8</v>
       </c>
-      <c r="F60" s="10" t="n">
-        <v>5</v>
+      <c r="F60" s="9" t="n">
+        <v>9</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2427,7 +2414,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>3.5-9.0</t>
+          <t>ratio=1.12 (0.44-2.00)</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2454,8 +2441,8 @@
       <c r="E61" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="F61" s="10" t="n">
-        <v>23</v>
+      <c r="F61" s="9" t="n">
+        <v>14</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2464,7 +2451,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>9.0-35.8</t>
+          <t>ratio=0.47 (0.30-1.03)</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2491,8 +2478,8 @@
       <c r="E62" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F62" s="10" t="n">
-        <v>9</v>
+      <c r="F62" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2501,7 +2488,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>1.0-11.0</t>
+          <t>ratio=1.00 (0.80-2.20)</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2528,8 +2515,8 @@
       <c r="E63" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="10" t="n">
-        <v>1</v>
+      <c r="F63" s="9" t="n">
+        <v>1.2</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2538,7 +2525,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.25 (0.50-1.50)</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2582,7 +2569,7 @@
       <c r="E65" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F65" s="10" t="n">
+      <c r="F65" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
@@ -2592,7 +2579,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>1.5-3.0</t>
+          <t>ratio=2.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2617,17 +2604,15 @@
         </is>
       </c>
       <c r="E66" s="8" t="n"/>
-      <c r="F66" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2652,17 +2637,15 @@
         </is>
       </c>
       <c r="E67" s="8" t="n"/>
-      <c r="F67" s="9" t="n">
-        <v>2</v>
-      </c>
+      <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2690,12 +2673,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2744,12 +2727,12 @@
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=0.75 (n=2)</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2776,8 +2759,8 @@
       <c r="E71" s="8" t="n">
         <v>12</v>
       </c>
-      <c r="F71" s="10" t="n">
-        <v>14.5</v>
+      <c r="F71" s="9" t="n">
+        <v>14.8</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
@@ -2786,7 +2769,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>2.0-18.8</t>
+          <t>ratio=1.23 (0.20-1.56)</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2814,12 +2797,12 @@
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2847,12 +2830,12 @@
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2879,8 +2862,8 @@
       <c r="E74" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F74" s="10" t="n">
-        <v>1.5</v>
+      <c r="F74" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
@@ -2889,7 +2872,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.25-1.50)</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2917,12 +2900,12 @@
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2950,12 +2933,12 @@
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -3000,16 +2983,16 @@
         <v>3</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>4.0-6.5</t>
+          <t>ratio=2.17 (n=2)</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3037,12 +3020,12 @@
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3069,7 +3052,7 @@
       <c r="E80" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F80" s="10" t="n">
+      <c r="F80" s="9" t="n">
         <v>8</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -3079,7 +3062,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>5.0-18.0</t>
+          <t>ratio=1.60 (1.60-1.60)</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3093,7 +3076,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>430.3</v>
+        <v>395.5</v>
       </c>
     </row>
   </sheetData>
@@ -3161,7 +3144,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-059, 25-058, 25-063, 25-071, 25-067</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5133,35 +5116,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-059</t>
+          <t>25-071</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-058</t>
+          <t>25-070</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-063</t>
+          <t>25-065</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-071</t>
+          <t>25-063</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-067</t>
+          <t>25-062</t>
         </is>
       </c>
     </row>
@@ -5216,23 +5199,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5250,19 +5229,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5276,7 +5251,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5285,12 +5260,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=0.21 (0.20-0.25)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5315,12 +5290,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.5-4.5</t>
+          <t>ratio=0.50 (0.20-0.50)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5345,12 +5320,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.00 (0.83-1.00)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5341,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25.5</v>
+        <v>24.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5375,12 +5350,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.5-30.0</t>
+          <t>ratio=0.82 (0.48-0.94)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5396,7 +5371,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5405,12 +5380,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.2-21.5</t>
+          <t>ratio=0.44 (0.41-0.54)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5401,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5435,12 +5410,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9.0-19.0</t>
+          <t>ratio=0.75 (0.55-0.95)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5431,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5465,12 +5440,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>8.0-12.0</t>
+          <t>ratio=1.38 (1.00-1.75)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5495,12 +5470,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5491,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5525,12 +5500,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.0-10.0</t>
+          <t>ratio=0.80 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5555,12 +5530,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-070, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5585,12 +5560,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5585,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5636,7 +5607,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5645,12 +5616,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4.5-8.0</t>
+          <t>ratio=0.67 (0.50-1.11)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5637,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5675,12 +5646,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3.0-10.0</t>
+          <t>ratio=0.54 (0.25-0.83)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5667,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5705,12 +5676,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.0-16.5</t>
+          <t>ratio=0.44 (0.20-0.89)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5726,23 +5697,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5756,7 +5723,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5765,12 +5732,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=3.00 (2.00-3.50)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5795,12 +5762,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-063</t>
         </is>
       </c>
     </row>
@@ -5825,12 +5792,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5855,12 +5822,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5.0-6.0</t>
+          <t>ratio=1.00 (0.67-1.33)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5876,23 +5843,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5915,12 +5878,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.0-5.5</t>
+          <t>ratio=2.00 (1.00-5.00)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5899,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5945,12 +5908,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-062</t>
         </is>
       </c>
     </row>
@@ -5975,12 +5938,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6000,17 +5963,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.00 (n=2)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6026,7 +5989,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6035,12 +5998,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3.0-5.0</t>
+          <t>ratio=1.00 (0.60-1.00)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6056,7 +6019,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6065,12 +6028,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2.0-11.0</t>
+          <t>ratio=0.70 (0.40-1.10)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6086,7 +6049,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6095,12 +6058,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.0-8.0</t>
+          <t>ratio=0.81 (0.38-1.00)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6079,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6125,12 +6088,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5-3.0</t>
+          <t>ratio=0.92 (0.67-1.00)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6109,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.8</v>
+        <v>2</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6155,12 +6118,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.8-5.5</t>
+          <t>ratio=0.33 (0.29-0.67)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-063</t>
         </is>
       </c>
     </row>
@@ -6180,19 +6143,15 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6206,7 +6165,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6215,12 +6174,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.0-9.5</t>
+          <t>ratio=1.62 (0.75-2.75)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6195,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6245,12 +6204,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>7.5-16.0</t>
+          <t>ratio=1.22 (0.94-1.50)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6225,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6275,12 +6234,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>13.0-27.0</t>
+          <t>ratio=0.76 (0.67-1.64)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6296,7 +6255,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6305,12 +6264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4.0-6.0</t>
+          <t>ratio=0.79 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6285,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>26</v>
+        <v>24.5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6335,12 +6294,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>8.0-28.0</t>
+          <t>ratio=0.68 (0.20-0.72)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6356,23 +6315,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6395,12 +6350,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.0-11.0</t>
+          <t>ratio=1.40 (0.80-2.20)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6371,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6425,12 +6380,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>10.5-58.0</t>
+          <t>ratio=0.88 (0.50-1.17)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6401,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6455,12 +6410,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>26.0-89.0</t>
+          <t>ratio=1.75 (1.30-2.02)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6431,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,12 +6440,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.33 (0.33-0.33)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-062</t>
         </is>
       </c>
     </row>
@@ -6506,7 +6461,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>50.5</v>
+        <v>49.8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6515,12 +6470,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>42.0-72.0</t>
+          <t>ratio=1.04 (0.88-1.23)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6491,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6545,12 +6500,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>15.0-27.0</t>
+          <t>ratio=0.66 (0.34-0.78)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6566,7 +6521,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6575,12 +6530,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>3.5-9.0</t>
+          <t>ratio=1.12 (0.44-2.00)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6596,7 +6551,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6605,12 +6560,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9.0-35.8</t>
+          <t>ratio=0.47 (0.30-1.03)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6581,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6635,12 +6590,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.0-11.0</t>
+          <t>ratio=1.00 (0.80-2.20)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6611,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6665,12 +6620,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.25 (0.50-1.50)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6695,12 +6650,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.5-3.0</t>
+          <t>ratio=2.00 (2.00-5.00)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063</t>
         </is>
       </c>
     </row>
@@ -6716,23 +6671,19 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6746,23 +6697,19 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>global:2.0-2.0</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6780,19 +6727,15 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6810,17 +6753,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=0.75 (n=2)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-062</t>
         </is>
       </c>
     </row>
@@ -6836,7 +6779,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6845,12 +6788,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2.0-18.8</t>
+          <t>ratio=1.23 (0.20-1.56)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6870,19 +6813,15 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6900,19 +6839,15 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6926,7 +6861,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6935,12 +6870,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.25-1.50)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-071, 25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -6960,19 +6895,15 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6990,19 +6921,15 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7016,21 +6943,21 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>4.0-6.5</t>
+          <t>ratio=2.17 (n=2)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-063, 25-062</t>
         </is>
       </c>
     </row>
@@ -7050,19 +6977,15 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>25-058, 25-059, 25-063, 25-067, 25-071</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7085,12 +7008,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>5.0-18.0</t>
+          <t>ratio=1.60 (1.60-1.60)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>25-071, 25-067, 25-063, 25-059, 25-058</t>
+          <t>25-065, 25-063, 25-062</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-069 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-069 GENERATED BUILD PLAN.xlsx
@@ -80,8 +80,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -631,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -664,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.21 (0.20-0.25)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>3</v>
+        <v>17.7</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.20-0.50)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -788,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.00)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I11" s="8" t="n"/>
@@ -825,7 +825,7 @@
         <v>30</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>24.5</v>
+        <v>4.1</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.82 (0.48-0.94)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -879,7 +879,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>17.5</v>
+        <v>28.3</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.44 (0.41-0.54)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -916,7 +916,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.55-0.95)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -970,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.38 (1.00-1.75)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.50-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1098,7 +1098,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1152,7 +1152,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1189,12 +1189,12 @@
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I24" s="8" t="n"/>
@@ -1222,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.50-1.11)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1259,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.54 (0.25-0.83)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.44 (0.20-0.89)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1350,12 +1350,12 @@
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H29" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I29" s="8" t="n"/>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-3.50)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.33)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1548,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-5.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1584,17 +1584,17 @@
       <c r="E36" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="10" t="n">
-        <v>1</v>
+      <c r="F36" s="9" t="n">
+        <v>0.2</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H37" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I37" s="8" t="n"/>
@@ -1658,17 +1658,17 @@
       <c r="E38" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>2</v>
+      <c r="F38" s="9" t="n">
+        <v>1.8</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.60-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>5</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.70 (0.40-1.10)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1787,7 +1787,7 @@
         <v>8</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.38-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.67-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1861,7 +1861,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.33 (0.29-0.67)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1915,12 +1915,12 @@
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H46" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I46" s="8" t="n"/>
@@ -1948,7 +1948,7 @@
         <v>4</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>6.5</v>
+        <v>22</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.75-2.75)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1985,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>9.800000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.22 (0.94-1.50)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2022,7 +2022,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.76 (0.67-1.64)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2059,7 +2059,7 @@
         <v>6</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.50-1.00)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2096,7 +2096,7 @@
         <v>36</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>24.5</v>
+        <v>8.9</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.68 (0.20-0.72)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2133,12 +2133,12 @@
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2166,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>7</v>
+        <v>13.2</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.80-2.20)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I53" s="8" t="n"/>
@@ -2203,7 +2203,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.17)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2240,7 +2240,7 @@
         <v>20</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>35</v>
+        <v>30.6</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.75 (1.30-2.02)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2276,17 +2276,17 @@
       <c r="E56" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F56" s="9" t="n">
-        <v>1</v>
+      <c r="F56" s="10" t="n">
+        <v>3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.33 (0.33-0.33)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2331,7 +2331,7 @@
         <v>48</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>49.8</v>
+        <v>24.5</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.88-1.23)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2368,7 +2368,7 @@
         <v>32</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>21</v>
+        <v>30.5</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.66 (0.34-0.78)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>9</v>
+        <v>15.2</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.44-2.00)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2442,7 +2442,7 @@
         <v>30</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>14</v>
+        <v>30.3</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.47 (0.30-1.03)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2479,7 +2479,7 @@
         <v>5</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-2.20)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2516,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="9" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="G63" s="8" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.50-1.50)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2570,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (2.00-5.00)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2607,12 +2607,12 @@
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I66" s="8" t="n"/>
@@ -2640,12 +2640,12 @@
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I67" s="8" t="n"/>
@@ -2673,12 +2673,12 @@
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I68" s="8" t="n"/>
@@ -2722,17 +2722,17 @@
       <c r="E70" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F70" s="10" t="n">
-        <v>1.5</v>
+      <c r="F70" s="9" t="n">
+        <v>2.1</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=2)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2760,7 +2760,7 @@
         <v>12</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>14.8</v>
+        <v>10.1</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.23 (0.20-1.56)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2797,12 +2797,12 @@
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I72" s="8" t="n"/>
@@ -2830,12 +2830,12 @@
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I73" s="8" t="n"/>
@@ -2863,7 +2863,7 @@
         <v>2</v>
       </c>
       <c r="F74" s="9" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-1.50)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2900,12 +2900,12 @@
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I75" s="8" t="n"/>
@@ -2933,12 +2933,12 @@
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I76" s="8" t="n"/>
@@ -2982,17 +2982,17 @@
       <c r="E78" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F78" s="10" t="n">
-        <v>6.5</v>
+      <c r="F78" s="9" t="n">
+        <v>3.3</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.17 (n=2)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3020,12 +3020,12 @@
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I79" s="8" t="n"/>
@@ -3053,7 +3053,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.60 (1.60-1.60)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>395.5</v>
+        <v>396.4</v>
       </c>
     </row>
   </sheetData>
@@ -5203,15 +5203,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5229,15 +5233,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5251,7 +5259,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5260,12 +5268,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=0.21 (0.20-0.25)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5289,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>17.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5290,12 +5298,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.20-0.50)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5319,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5320,12 +5328,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.83-1.00)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5349,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.5</v>
+        <v>4.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -5350,12 +5358,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.82 (0.48-0.94)</t>
+          <t>group_total:33h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -5371,7 +5379,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>17.5</v>
+        <v>28.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5380,12 +5388,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=0.44 (0.41-0.54)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5409,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>15</v>
+        <v>6.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5410,12 +5418,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=0.75 (0.55-0.95)</t>
+          <t>group_total:35h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5439,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5440,12 +5448,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ratio=1.38 (1.00-1.75)</t>
+          <t>group_total:8h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5469,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5470,12 +5478,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5491,7 +5499,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5500,12 +5508,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ratio=0.80 (0.50-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5521,7 +5529,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>4.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5530,12 +5538,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-070, 25-063, 25-062</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5559,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5560,12 +5568,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5585,15 +5593,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5607,7 +5619,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5616,12 +5628,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=0.67 (0.50-1.11)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5637,7 +5649,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5646,12 +5658,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ratio=0.54 (0.25-0.83)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5679,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5676,12 +5688,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=0.44 (0.20-0.89)</t>
+          <t>group_total:22h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SHELLS)</t>
         </is>
       </c>
     </row>
@@ -5701,15 +5713,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -5723,7 +5739,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5732,12 +5748,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ratio=3.00 (2.00-3.50)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5769,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5762,12 +5778,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-063</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5783,7 +5799,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5792,12 +5808,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5829,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5822,12 +5838,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.33)</t>
+          <t>group_total:7h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5847,15 +5863,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5869,7 +5889,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5878,12 +5898,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-5.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5899,21 +5919,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-062</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5938,12 +5958,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-063, 25-062</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5959,21 +5979,21 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=2)</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-063, 25-062</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -5989,7 +6009,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5998,12 +6018,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.60-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SKIRT)</t>
         </is>
       </c>
     </row>
@@ -6019,7 +6039,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6028,12 +6048,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=0.70 (0.40-1.10)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SKIRT)</t>
         </is>
       </c>
     </row>
@@ -6049,7 +6069,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6058,12 +6078,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=0.81 (0.38-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(SKIRT)</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6099,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.8</v>
+        <v>4.7</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6088,12 +6108,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ratio=0.92 (0.67-1.00)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(SKIRT)</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6129,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6118,12 +6138,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ratio=0.33 (0.29-0.67)</t>
+          <t>group_total:25h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-063</t>
+          <t>model(SKIRT)</t>
         </is>
       </c>
     </row>
@@ -6143,15 +6163,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6165,7 +6189,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6.5</v>
+        <v>22</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6174,12 +6198,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.62 (0.75-2.75)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6219,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>9.800000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6204,12 +6228,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ratio=1.22 (0.94-1.50)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6249,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>13.8</v>
+        <v>15.1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6234,12 +6258,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>ratio=0.76 (0.67-1.64)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6255,7 +6279,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6264,12 +6288,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=0.79 (0.50-1.00)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6285,7 +6309,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>24.5</v>
+        <v>8.9</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6294,12 +6318,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>ratio=0.68 (0.20-0.72)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6319,15 +6343,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6341,7 +6369,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>13.2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6350,12 +6378,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ratio=1.40 (0.80-2.20)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6371,7 +6399,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10.5</v>
+        <v>6.7</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6380,12 +6408,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=0.88 (0.50-1.17)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6429,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>35</v>
+        <v>30.6</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6410,12 +6438,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ratio=1.75 (1.30-2.02)</t>
+          <t>group_total:114h</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -6431,21 +6459,21 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ratio=0.33 (0.33-0.33)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-062</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6489,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>49.8</v>
+        <v>24.5</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6470,12 +6498,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ratio=1.04 (0.88-1.23)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6519,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>21</v>
+        <v>30.5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6500,12 +6528,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ratio=0.66 (0.34-0.78)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6521,7 +6549,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9</v>
+        <v>15.2</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6530,12 +6558,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ratio=1.12 (0.44-2.00)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6551,7 +6579,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>14</v>
+        <v>30.3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6560,12 +6588,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ratio=0.47 (0.30-1.03)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25-071, 25-070, 25-065, 25-063, 25-062</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6581,7 +6609,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6590,12 +6618,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.80-2.20)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6639,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6620,12 +6648,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.50-1.50)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6669,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6650,12 +6678,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ratio=2.00 (2.00-5.00)</t>
+          <t>group_total:115h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -6675,15 +6703,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6701,15 +6733,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6727,15 +6763,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6749,21 +6789,21 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ratio=0.75 (n=2)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>25-071, 25-062</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6779,7 +6819,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>14.8</v>
+        <v>10.1</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6788,12 +6828,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ratio=1.23 (0.20-1.56)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6813,15 +6853,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6839,15 +6883,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6861,7 +6909,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6870,12 +6918,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.25-1.50)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25-071, 25-065, 25-063, 25-062</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6895,15 +6943,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6921,15 +6973,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6943,21 +6999,21 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ratio=2.17 (n=2)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>25-063, 25-062</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -6977,15 +7033,19 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6999,7 +7059,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7008,12 +7068,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>ratio=1.60 (1.60-1.60)</t>
+          <t>group_total:20h</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>25-065, 25-063, 25-062</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-069 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-069 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         <v>6</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         <v>40</v>
       </c>
       <c r="F14" s="9" t="n">
-        <v>28.3</v>
+        <v>27.5</v>
       </c>
       <c r="G14" s="8" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I14" s="8" t="n"/>
@@ -916,7 +916,7 @@
         <v>20</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -970,7 +970,7 @@
         <v>8</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1024,7 +1024,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1222,7 +1222,7 @@
         <v>9</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1259,7 +1259,7 @@
         <v>12</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1296,7 +1296,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1383,7 +1383,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1420,7 +1420,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1494,7 +1494,7 @@
         <v>6</v>
       </c>
       <c r="F33" s="9" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1548,7 +1548,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G37" s="8" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>2</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>5</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1750,7 +1750,7 @@
         <v>5</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1787,7 +1787,7 @@
         <v>8</v>
       </c>
       <c r="F42" s="9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I42" s="8" t="n"/>
@@ -1824,7 +1824,7 @@
         <v>3</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1861,7 +1861,7 @@
         <v>6</v>
       </c>
       <c r="F44" s="9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G44" s="8" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1985,7 +1985,7 @@
         <v>8</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -2022,7 +2022,7 @@
         <v>18</v>
       </c>
       <c r="F49" s="9" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="G49" s="8" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>5</v>
       </c>
       <c r="F53" s="9" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>12</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>20</v>
       </c>
       <c r="F55" s="9" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="G55" s="8" t="inlineStr">
         <is>
@@ -2331,7 +2331,7 @@
         <v>48</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="G58" s="8" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I58" s="8" t="n"/>
@@ -2368,7 +2368,7 @@
         <v>32</v>
       </c>
       <c r="F59" s="9" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="G59" s="8" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H59" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I59" s="8" t="n"/>
@@ -2405,7 +2405,7 @@
         <v>8</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="G60" s="8" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="H60" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I60" s="8" t="n"/>
@@ -2442,7 +2442,7 @@
         <v>30</v>
       </c>
       <c r="F61" s="9" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="G61" s="8" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H61" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I61" s="8" t="n"/>
@@ -2479,7 +2479,7 @@
         <v>5</v>
       </c>
       <c r="F62" s="9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G62" s="8" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="H62" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I62" s="8" t="n"/>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I63" s="8" t="n"/>
@@ -2570,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G65" s="8" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="I65" s="8" t="n"/>
@@ -2723,7 +2723,7 @@
         <v>2</v>
       </c>
       <c r="F70" s="9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G70" s="8" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I70" s="8" t="n"/>
@@ -2760,7 +2760,7 @@
         <v>12</v>
       </c>
       <c r="F71" s="9" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="G71" s="8" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I71" s="8" t="n"/>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I74" s="8" t="n"/>
@@ -2983,7 +2983,7 @@
         <v>3</v>
       </c>
       <c r="F78" s="9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I78" s="8" t="n"/>
@@ -3053,7 +3053,7 @@
         <v>5</v>
       </c>
       <c r="F80" s="9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="I80" s="8" t="n"/>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="F82" s="1" t="n">
-        <v>396.4</v>
+        <v>399.4</v>
       </c>
     </row>
   </sheetData>
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>28.3</v>
+        <v>27.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -5409,7 +5409,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:35h</t>
+          <t>group_total:34h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -5439,7 +5439,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>group_total:8h</t>
+          <t>group_total:9h</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -5499,7 +5499,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5619,7 +5619,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5679,7 +5679,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9.199999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:22h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5739,7 +5739,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -5769,7 +5769,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>group_total:7h</t>
+          <t>group_total:10h</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -5889,7 +5889,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5949,7 +5949,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5979,7 +5979,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6099,7 +6099,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>group_total:25h</t>
+          <t>group_total:24h</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6219,7 +6219,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>12.8</v>
+        <v>12.7</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6489,7 +6489,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6519,7 +6519,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>30.3</v>
+        <v>30.6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6609,7 +6609,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>group_total:115h</t>
+          <t>group_total:116h</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6999,7 +6999,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>group_total:20h</t>
+          <t>group_total:19h</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
